--- a/reportes/templates/template_reporte.xlsx
+++ b/reportes/templates/template_reporte.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cardex-inventario\reportes\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f93473b447390d20/Desktop/cardex-inventario/reportes/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB61F07-E0BB-47BC-9466-318C221A0110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{1EB61F07-E0BB-47BC-9466-318C221A0110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44BAF45F-9F62-44F8-91AE-147FB26C7C88}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Template!$A$1:$I$1000</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Template!$A$1:$I$989</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -102,12 +103,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -175,19 +170,20 @@
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="26"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -214,27 +210,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="14">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -384,130 +365,131 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -565,20 +547,25 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>0</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2057400" cy="714374"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Image 1" descr="Picture">
+        <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49BB955A-9B59-4A35-8136-88C9909D60AE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{934ACC6C-367D-4442-9909-6C4678ADE6DB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -592,7 +579,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19050" y="1"/>
+          <a:off x="19050" y="3381376"/>
           <a:ext cx="2057400" cy="714374"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -603,6 +590,10 @@
     <xdr:clientData/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -890,7 +881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -905,577 +896,173 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27"/>
-      <c r="B1" s="28"/>
-      <c r="C1" s="17" t="s">
+      <c r="A1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="3" t="s">
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="4"/>
+      <c r="J1" s="2"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="3" t="s">
+      <c r="A2" s="20"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="4"/>
+      <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="31"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="5" t="s">
+      <c r="A3" s="22"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="4"/>
+      <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:10" ht="3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
     </row>
     <row r="5" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="33" t="s">
+      <c r="B5" s="26"/>
+      <c r="C5" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="4"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:10" ht="3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="7">
+      <c r="B7" s="28"/>
+      <c r="C7" s="5">
         <v>46111</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="26" t="s">
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="4"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="2"/>
     </row>
     <row r="8" spans="1:10" ht="3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="4" t="s">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
     </row>
     <row r="10" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-    </row>
-    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="12"/>
-    </row>
-    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="2"/>
-    </row>
-    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="2"/>
-    </row>
-    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="2"/>
-    </row>
-    <row r="23" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A23" s="27"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="J23" s="4"/>
-    </row>
-    <row r="24" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A24" s="29"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J24" s="4"/>
-    </row>
-    <row r="25" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A25" s="31"/>
-      <c r="B25" s="32"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="J25" s="4"/>
-    </row>
-    <row r="26" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-    </row>
-    <row r="27" spans="1:10" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A27" s="35" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" s="36"/>
-      <c r="C27" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="33"/>
-      <c r="J27" s="4"/>
-    </row>
-    <row r="28" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-    </row>
-    <row r="29" spans="1:10" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A29" s="34" t="s">
-        <v>5</v>
-      </c>
-      <c r="B29" s="34"/>
-      <c r="C29" s="7">
-        <v>46111</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="4"/>
-    </row>
-    <row r="30" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-    </row>
-    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.4">
-      <c r="A31" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-    </row>
-    <row r="32" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="13"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="12"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="2"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="2"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="2"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="2"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="2"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="2"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="2"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="2"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="2"/>
+    <row r="22" spans="10:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="10:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="10:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="10:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="J29" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="A23:B25"/>
-    <mergeCell ref="C23:H25"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:I27"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
+  <mergeCells count="8">
     <mergeCell ref="A9:I9"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="C1:H3"/>
@@ -1488,4 +1075,191 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F17F10B2-5D1C-403A-9752-19CBD3A5A6DE}">
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" customWidth="1"/>
+    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.140625" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="1.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A5" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="26"/>
+      <c r="C5" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A7" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="28"/>
+      <c r="C7" s="5">
+        <v>46111</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:H3"/>
+    <mergeCell ref="A1:B3"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:I7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>